--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALFINDÉN CB.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_ALFINDÉN CB.xlsx
@@ -565,13 +565,13 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9055</v>
+        <v>1.2488</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7442</v>
+        <v>3.8147</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8387</v>
+        <v>-2.565500000000001</v>
       </c>
       <c r="G2" t="n">
         <v>-4.3153</v>
@@ -610,13 +610,13 @@
         <v>11.1096</v>
       </c>
       <c r="S2" t="n">
-        <v>4.39</v>
+        <v>2.7335</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6819</v>
+        <v>1.7522</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7082</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7403000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6807</v>
+        <v>0.5965</v>
       </c>
       <c r="E3" t="n">
         <v>-0.0422</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7228</v>
+        <v>0.6387</v>
       </c>
       <c r="G3" t="n">
         <v>0.2267</v>
@@ -688,13 +688,13 @@
         <v>0.1984</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2556</v>
+        <v>0.1714</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.318</v>
+        <v>0.2338</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7328</v>
@@ -766,13 +766,13 @@
         <v>0.1984</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.0708</v>
+        <v>-3.9807</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2385</v>
+        <v>-1.6434</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8324</v>
+        <v>-2.3373</v>
       </c>
       <c r="G5" t="n">
         <v>0.5077</v>
@@ -844,13 +844,13 @@
         <v>2.7774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9716</v>
+        <v>-0.8814000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.748</v>
+        <v>-0.1528</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2236</v>
+        <v>-0.7285999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-2.2182</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.032</v>
+        <v>-6.311699999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-14.4707</v>
+        <v>1.8689</v>
       </c>
       <c r="F6" t="n">
-        <v>8.439</v>
+        <v>-8.180400000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.436599999999999</v>
+        <v>-27.1976</v>
       </c>
       <c r="H6" t="n">
-        <v>1.337699999999999</v>
+        <v>-2.8004</v>
       </c>
       <c r="I6" t="n">
-        <v>-7.774</v>
+        <v>-24.3972</v>
       </c>
       <c r="J6" t="n">
-        <v>30.7238</v>
+        <v>13.0991</v>
       </c>
       <c r="K6" t="n">
-        <v>19.1446</v>
+        <v>18.0845</v>
       </c>
       <c r="L6" t="n">
-        <v>11.5793</v>
+        <v>-4.985699999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-37.1602</v>
+        <v>-40.2964</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.8069</v>
+        <v>-20.8846</v>
       </c>
       <c r="O6" t="n">
-        <v>-19.3534</v>
+        <v>-19.4116</v>
       </c>
       <c r="P6" t="n">
-        <v>-33.5269</v>
+        <v>-20.4336</v>
       </c>
       <c r="Q6" t="n">
-        <v>-75.9811</v>
+        <v>-64.2765</v>
       </c>
       <c r="R6" t="n">
-        <v>42.4538</v>
+        <v>43.8427</v>
       </c>
       <c r="S6" t="n">
-        <v>37.5437</v>
+        <v>-5.8961</v>
       </c>
       <c r="T6" t="n">
-        <v>19.8816</v>
+        <v>-4.2939</v>
       </c>
       <c r="U6" t="n">
-        <v>17.662</v>
+        <v>-1.6022</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.611799999999999</v>
+        <v>47.2155</v>
       </c>
       <c r="W6" t="n">
-        <v>10.9054</v>
+        <v>57.3403</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.5173</v>
+        <v>-10.1245</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>-11.46</v>
+        <v>-8.1166</v>
       </c>
       <c r="E7" t="n">
-        <v>-13.5775</v>
+        <v>8.293899999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1174</v>
+        <v>-16.4112</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.8342</v>
+        <v>-18.5815</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3532</v>
+        <v>-11.1959</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.481</v>
+        <v>-7.3855</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9808</v>
+        <v>30.362</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1272999999999999</v>
+        <v>16.3613</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.108</v>
+        <v>14.0012</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.8533</v>
+        <v>-48.9439</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.4806</v>
+        <v>-27.5571</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3729</v>
+        <v>-21.3868</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.182</v>
+        <v>1.1902</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.332000000000001</v>
+        <v>-50.3893</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1501</v>
+        <v>51.5798</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1776</v>
+        <v>-8.0913</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.2644</v>
+        <v>-6.7703</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0868</v>
+        <v>-1.3209</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.266</v>
+        <v>17.3654</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>35.0917</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-17.7264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PARDOS MARTINEZ</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>-20.8647</v>
+        <v>-9.7331</v>
       </c>
       <c r="E8" t="n">
-        <v>-14.8282</v>
+        <v>-12.2907</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.0364</v>
+        <v>2.5578</v>
       </c>
       <c r="G8" t="n">
-        <v>-19.7406</v>
+        <v>-6.8342</v>
       </c>
       <c r="H8" t="n">
-        <v>-12.9555</v>
+        <v>-3.3532</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.7853</v>
+        <v>-3.481</v>
       </c>
       <c r="J8" t="n">
-        <v>-7.0951</v>
+        <v>-1.9808</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.2658</v>
+        <v>0.1272999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1709000000000001</v>
+        <v>-2.108</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.6458</v>
+        <v>-4.8533</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.690099999999999</v>
+        <v>-3.4806</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.9562</v>
+        <v>-1.3729</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.190400000000001</v>
+        <v>-2.182</v>
       </c>
       <c r="Q8" t="n">
-        <v>-19.6398</v>
+        <v>-8.332000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>18.45</v>
+        <v>6.1501</v>
       </c>
       <c r="S8" t="n">
-        <v>7.5096</v>
+        <v>-0.4505</v>
       </c>
       <c r="T8" t="n">
-        <v>9.104699999999999</v>
+        <v>-1.9776</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.595</v>
+        <v>1.5271</v>
       </c>
       <c r="V8" t="n">
-        <v>-7.4428</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8025</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.2452</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>D. CORTES ALEJANDRE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>-21.7859</v>
+        <v>-24.0341</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.6038</v>
+        <v>-19.9181</v>
       </c>
       <c r="F9" t="n">
-        <v>-12.1824</v>
+        <v>-4.116000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-27.1976</v>
+        <v>-17.4734</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8004</v>
+        <v>-4.7377</v>
       </c>
       <c r="I9" t="n">
-        <v>-24.3972</v>
+        <v>-12.7357</v>
       </c>
       <c r="J9" t="n">
-        <v>13.0991</v>
+        <v>-10.0994</v>
       </c>
       <c r="K9" t="n">
-        <v>18.0845</v>
+        <v>0.8488</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.985699999999999</v>
+        <v>-10.9481</v>
       </c>
       <c r="M9" t="n">
-        <v>-40.2964</v>
+        <v>-7.3742</v>
       </c>
       <c r="N9" t="n">
-        <v>-20.8846</v>
+        <v>-5.5867</v>
       </c>
       <c r="O9" t="n">
-        <v>-19.4116</v>
+        <v>-1.7875</v>
       </c>
       <c r="P9" t="n">
-        <v>-20.4336</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-64.2765</v>
+        <v>-10.911</v>
       </c>
       <c r="R9" t="n">
-        <v>43.8427</v>
+        <v>8.728899999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-21.3704</v>
+        <v>-1.5077</v>
       </c>
       <c r="T9" t="n">
-        <v>-15.7663</v>
+        <v>0.4369</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.6041</v>
+        <v>-1.9445</v>
       </c>
       <c r="V9" t="n">
-        <v>47.2155</v>
+        <v>-2.8708</v>
       </c>
       <c r="W9" t="n">
-        <v>57.3403</v>
+        <v>0.6553999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-10.1245</v>
+        <v>-3.5261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-25.3736</v>
+        <v>-24.7601</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.247100000000001</v>
+        <v>-16.6041</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.1263</v>
+        <v>-8.156099999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-18.5815</v>
+        <v>-19.4264</v>
       </c>
       <c r="H10" t="n">
-        <v>-11.1959</v>
+        <v>-4.7624</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.3855</v>
+        <v>-14.6643</v>
       </c>
       <c r="J10" t="n">
-        <v>30.362</v>
+        <v>2.2742</v>
       </c>
       <c r="K10" t="n">
-        <v>16.3613</v>
+        <v>12.1594</v>
       </c>
       <c r="L10" t="n">
-        <v>14.0012</v>
+        <v>-9.885299999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-48.9439</v>
+        <v>-21.7007</v>
       </c>
       <c r="N10" t="n">
-        <v>-27.5571</v>
+        <v>-16.9215</v>
       </c>
       <c r="O10" t="n">
-        <v>-21.3868</v>
+        <v>-4.7793</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1902</v>
+        <v>10.3161</v>
       </c>
       <c r="Q10" t="n">
-        <v>-50.3893</v>
+        <v>-18.6479</v>
       </c>
       <c r="R10" t="n">
-        <v>51.5798</v>
+        <v>28.9642</v>
       </c>
       <c r="S10" t="n">
-        <v>-25.3479</v>
+        <v>-2.6088</v>
       </c>
       <c r="T10" t="n">
-        <v>-20.3116</v>
+        <v>-3.5126</v>
       </c>
       <c r="U10" t="n">
-        <v>-5.0363</v>
+        <v>0.9039</v>
       </c>
       <c r="V10" t="n">
-        <v>17.3654</v>
+        <v>-13.0413</v>
       </c>
       <c r="W10" t="n">
-        <v>35.0917</v>
+        <v>3.2822</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.7264</v>
+        <v>-16.3235</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>G. PARDOS MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>-26.3323</v>
+        <v>-27.5664</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.7142</v>
+        <v>-21.8171</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.618</v>
+        <v>-5.7492</v>
       </c>
       <c r="G11" t="n">
-        <v>-13.3518</v>
+        <v>-19.7406</v>
       </c>
       <c r="H11" t="n">
-        <v>1.191</v>
+        <v>-12.9555</v>
       </c>
       <c r="I11" t="n">
-        <v>-14.5426</v>
+        <v>-6.7853</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4754</v>
+        <v>-7.0951</v>
       </c>
       <c r="K11" t="n">
-        <v>8.890000000000001</v>
+        <v>-7.2658</v>
       </c>
       <c r="L11" t="n">
-        <v>-10.3654</v>
+        <v>0.1709000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-11.8763</v>
+        <v>-12.6458</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.699</v>
+        <v>-5.690099999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.1774</v>
+        <v>-6.9562</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.166</v>
+        <v>-1.190400000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-18.648</v>
+        <v>-19.6398</v>
       </c>
       <c r="R11" t="n">
-        <v>14.4822</v>
+        <v>18.45</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2046</v>
+        <v>0.8079999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>3.249</v>
+        <v>2.1156</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.0442</v>
+        <v>-1.3078</v>
       </c>
       <c r="V11" t="n">
-        <v>-10.0191</v>
+        <v>-7.4428</v>
       </c>
       <c r="W11" t="n">
-        <v>8.1601</v>
+        <v>2.8025</v>
       </c>
       <c r="X11" t="n">
-        <v>-18.1794</v>
+        <v>-10.2452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CORTES ALEJANDRE</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>-27.1913</v>
+        <v>-28.6181</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.1061</v>
+        <v>-11.6845</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0852</v>
+        <v>-16.9337</v>
       </c>
       <c r="G12" t="n">
-        <v>-17.4734</v>
+        <v>-13.3518</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.7377</v>
+        <v>1.191</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.7357</v>
+        <v>-14.5426</v>
       </c>
       <c r="J12" t="n">
-        <v>-10.0994</v>
+        <v>-1.4754</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8488</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-10.9481</v>
+        <v>-10.3654</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.3742</v>
+        <v>-11.8763</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.5867</v>
+        <v>-7.699</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7875</v>
+        <v>-4.1774</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1822</v>
+        <v>-4.166</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.911</v>
+        <v>-18.648</v>
       </c>
       <c r="R12" t="n">
-        <v>8.728899999999999</v>
+        <v>14.4822</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6648</v>
+        <v>-1.0812</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7511</v>
+        <v>0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.9137</v>
+        <v>-1.3601</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.8708</v>
+        <v>-10.0191</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6553999999999999</v>
+        <v>8.1601</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5261</v>
+        <v>-18.1794</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.8984</v>
+        <v>-30.9663</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.9335</v>
+        <v>-18.8823</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.9652</v>
+        <v>-12.0837</v>
       </c>
       <c r="G13" t="n">
         <v>-10.9344</v>
@@ -1468,13 +1468,13 @@
         <v>25.1949</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1515</v>
+        <v>0.7810000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3018999999999998</v>
+        <v>0.3528</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4537</v>
+        <v>0.4280000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-12.0836</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.3279</v>
+        <v>-31.2062</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.6023</v>
+        <v>-30.4441</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.7258</v>
+        <v>-0.7624000000000007</v>
       </c>
       <c r="G14" t="n">
-        <v>-19.4264</v>
+        <v>-6.436599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.7624</v>
+        <v>1.337699999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.6643</v>
+        <v>-7.774</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2742</v>
+        <v>30.7238</v>
       </c>
       <c r="K14" t="n">
-        <v>12.1594</v>
+        <v>19.1446</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.885299999999999</v>
+        <v>11.5793</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.7007</v>
+        <v>-37.1602</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.9215</v>
+        <v>-17.8069</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.7793</v>
+        <v>-19.3534</v>
       </c>
       <c r="P14" t="n">
-        <v>10.3161</v>
+        <v>-33.5269</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.6479</v>
+        <v>-75.9811</v>
       </c>
       <c r="R14" t="n">
-        <v>28.9642</v>
+        <v>42.4538</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.1764</v>
+        <v>12.369</v>
       </c>
       <c r="T14" t="n">
-        <v>-11.5099</v>
+        <v>3.9079</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6659</v>
+        <v>8.460699999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-13.0413</v>
+        <v>-3.611799999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2822</v>
+        <v>10.9054</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.3235</v>
+        <v>-14.5173</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GOMES CORREIA</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-40.4315</v>
+        <v>-38.4795</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.3869</v>
+        <v>-34.0484</v>
       </c>
       <c r="F15" t="n">
-        <v>-21.0448</v>
+        <v>-4.4311</v>
       </c>
       <c r="G15" t="n">
-        <v>-16.9196</v>
+        <v>-14.2044</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.152699999999999</v>
+        <v>-10.8162</v>
       </c>
       <c r="I15" t="n">
-        <v>-11.7669</v>
+        <v>-3.3882</v>
       </c>
       <c r="J15" t="n">
-        <v>14.7258</v>
+        <v>7.761200000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>13.8694</v>
+        <v>1.8618</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8564999999999999</v>
+        <v>5.8995</v>
       </c>
       <c r="M15" t="n">
-        <v>-31.6456</v>
+        <v>-21.9658</v>
       </c>
       <c r="N15" t="n">
-        <v>-19.0222</v>
+        <v>-12.678</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.6232</v>
+        <v>-9.287800000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-22.4174</v>
+        <v>-17.6563</v>
       </c>
       <c r="Q15" t="n">
-        <v>-56.5394</v>
+        <v>-43.0493</v>
       </c>
       <c r="R15" t="n">
-        <v>34.122</v>
+        <v>25.3931</v>
       </c>
       <c r="S15" t="n">
-        <v>7.782100000000001</v>
+        <v>2.0971</v>
       </c>
       <c r="T15" t="n">
-        <v>7.0139</v>
+        <v>1.2259</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7681999999999998</v>
+        <v>0.8710000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.8765</v>
+        <v>-8.716099999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>15.4129</v>
+        <v>0.01409999999999989</v>
       </c>
       <c r="X15" t="n">
-        <v>-24.2894</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>A. GOMES CORREIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>-40.7818</v>
+        <v>-43.6124</v>
       </c>
       <c r="E16" t="n">
-        <v>-35.692</v>
+        <v>-24.9987</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.0893</v>
+        <v>-18.614</v>
       </c>
       <c r="G16" t="n">
-        <v>-14.2044</v>
+        <v>-16.9196</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.8162</v>
+        <v>-5.152699999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.3882</v>
+        <v>-11.7669</v>
       </c>
       <c r="J16" t="n">
-        <v>7.761200000000001</v>
+        <v>14.7258</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8618</v>
+        <v>13.8694</v>
       </c>
       <c r="L16" t="n">
-        <v>5.8995</v>
+        <v>0.8564999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-21.9658</v>
+        <v>-31.6456</v>
       </c>
       <c r="N16" t="n">
-        <v>-12.678</v>
+        <v>-19.0222</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.287800000000001</v>
+        <v>-12.6232</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.6563</v>
+        <v>-22.4174</v>
       </c>
       <c r="Q16" t="n">
-        <v>-43.0493</v>
+        <v>-56.5394</v>
       </c>
       <c r="R16" t="n">
-        <v>25.3931</v>
+        <v>34.122</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2046</v>
+        <v>4.601</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4179000000000002</v>
+        <v>1.4024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2132999999999998</v>
+        <v>3.199</v>
       </c>
       <c r="V16" t="n">
-        <v>-8.716099999999999</v>
+        <v>-8.8765</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01409999999999989</v>
+        <v>15.4129</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.73</v>
+        <v>-24.2894</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-81.5774</v>
+        <v>-72.288</v>
       </c>
       <c r="E17" t="n">
-        <v>-46.1846</v>
+        <v>-41.6784</v>
       </c>
       <c r="F17" t="n">
-        <v>-35.3931</v>
+        <v>-30.6096</v>
       </c>
       <c r="G17" t="n">
         <v>-24.0391</v>
@@ -1780,13 +1780,13 @@
         <v>32.3368</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.5182</v>
+        <v>-5.2292</v>
       </c>
       <c r="T17" t="n">
-        <v>-6.1026</v>
+        <v>-1.5963</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.4155</v>
+        <v>-3.6323</v>
       </c>
       <c r="V17" t="n">
         <v>-19.4125</v>
@@ -1813,19 +1813,19 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-372.1931</v>
+        <v>-348.4516</v>
       </c>
       <c r="E18" t="n">
-        <v>-230.8834</v>
+        <v>-220.0745</v>
       </c>
       <c r="F18" t="n">
-        <v>-141.3101</v>
+        <v>-128.3774</v>
       </c>
       <c r="G18" t="n">
         <v>-199.4533</v>
       </c>
       <c r="H18" t="n">
-        <v>-50.9458</v>
+        <v>-50.94580000000001</v>
       </c>
       <c r="I18" t="n">
         <v>-148.5069</v>
@@ -1858,16 +1858,16 @@
         <v>345.9823</v>
       </c>
       <c r="S18" t="n">
-        <v>-26.01469999999999</v>
+        <v>-2.274500000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>-17.7011</v>
+        <v>-6.893299999999998</v>
       </c>
       <c r="U18" t="n">
-        <v>-8.312800000000001</v>
+        <v>4.619199999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-24.7181</v>
+        <v>-24.71809999999999</v>
       </c>
       <c r="W18" t="n">
         <v>149.5518</v>
